--- a/Ejemplo/2025-Notas evaluaciones Auditoria_Gerente y Socios.xlsx
+++ b/Ejemplo/2025-Notas evaluaciones Auditoria_Gerente y Socios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f6a2ed62d12d53eb/Desktop/Espacio compartido/Control_formacion/Ejemplo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuyih\Documents\Github\Control_formacion\Ejemplo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{0A81073D-E259-4105-B6F8-0000AD633E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE087EE0-D309-4E48-A360-A51E6F280B17}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97762557-1305-440F-9EC4-31914F003286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="115">
   <si>
     <t>?</t>
   </si>
@@ -589,6 +589,9 @@
   </si>
   <si>
     <t>Jose Antonio Andujar Fernandez</t>
+  </si>
+  <si>
+    <t>Indice</t>
   </si>
 </sst>
 </file>
@@ -1219,7 +1222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1684,12 +1687,90 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1702,83 +1783,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1786,11 +1795,23 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1804,38 +1825,23 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5571,7 +5577,7 @@
     <col min="1" max="1" width="0" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="3.42578125" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="4" max="4" width="20" style="213" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
     <col min="7" max="7" width="30.28515625" customWidth="1"/>
@@ -5654,107 +5660,110 @@
       </c>
     </row>
     <row r="2" spans="3:70" ht="35.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J2" s="184"/>
-      <c r="K2" s="184"/>
-      <c r="L2" s="184"/>
-      <c r="M2" s="184"/>
-      <c r="N2" s="184"/>
-      <c r="O2" s="184"/>
-      <c r="P2" s="184"/>
-      <c r="Q2" s="184"/>
-      <c r="R2" s="184"/>
-      <c r="S2" s="184"/>
-      <c r="T2" s="184"/>
-      <c r="U2" s="184"/>
-      <c r="V2" s="185"/>
+      <c r="J2" s="164"/>
+      <c r="K2" s="164"/>
+      <c r="L2" s="164"/>
+      <c r="M2" s="164"/>
+      <c r="N2" s="164"/>
+      <c r="O2" s="164"/>
+      <c r="P2" s="164"/>
+      <c r="Q2" s="164"/>
+      <c r="R2" s="164"/>
+      <c r="S2" s="164"/>
+      <c r="T2" s="164"/>
+      <c r="U2" s="164"/>
+      <c r="V2" s="165"/>
       <c r="W2" s="4"/>
-      <c r="X2" s="186" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y2" s="188" t="s">
+      <c r="X2" s="166" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y2" s="168" t="s">
         <v>3</v>
       </c>
-      <c r="Z2" s="189"/>
-      <c r="AA2" s="190" t="s">
+      <c r="Z2" s="169"/>
+      <c r="AA2" s="170" t="s">
         <v>4</v>
       </c>
-      <c r="AB2" s="192" t="s">
+      <c r="AB2" s="172" t="s">
         <v>5</v>
       </c>
-      <c r="AC2" s="193"/>
-      <c r="AD2" s="181" t="s">
+      <c r="AC2" s="173"/>
+      <c r="AD2" s="162" t="s">
         <v>6</v>
       </c>
-      <c r="AE2" s="182"/>
+      <c r="AE2" s="163"/>
       <c r="AF2" s="176" t="s">
         <v>7</v>
       </c>
       <c r="AG2" s="177"/>
-      <c r="AH2" s="168" t="s">
+      <c r="AH2" s="178" t="s">
         <v>8</v>
       </c>
-      <c r="AI2" s="169"/>
-      <c r="AJ2" s="170" t="s">
+      <c r="AI2" s="179"/>
+      <c r="AJ2" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="AK2" s="178" t="s">
+      <c r="AK2" s="182" t="s">
         <v>10</v>
       </c>
-      <c r="AL2" s="179"/>
-      <c r="AM2" s="180"/>
-      <c r="AN2" s="181" t="s">
+      <c r="AL2" s="183"/>
+      <c r="AM2" s="184"/>
+      <c r="AN2" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="AO2" s="182"/>
+      <c r="AO2" s="163"/>
       <c r="AP2" s="176" t="s">
         <v>12</v>
       </c>
-      <c r="AQ2" s="183"/>
-      <c r="AR2" s="183"/>
+      <c r="AQ2" s="185"/>
+      <c r="AR2" s="185"/>
       <c r="AS2" s="177"/>
-      <c r="AT2" s="168" t="s">
+      <c r="AT2" s="178" t="s">
         <v>13</v>
       </c>
-      <c r="AU2" s="169"/>
-      <c r="AV2" s="170" t="s">
+      <c r="AU2" s="179"/>
+      <c r="AV2" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="AW2" s="172" t="s">
+      <c r="AW2" s="186" t="s">
         <v>14</v>
       </c>
-      <c r="AX2" s="172" t="s">
+      <c r="AX2" s="186" t="s">
         <v>15</v>
       </c>
-      <c r="AY2" s="174" t="s">
+      <c r="AY2" s="188" t="s">
         <v>16</v>
       </c>
-      <c r="AZ2" s="162" t="s">
+      <c r="AZ2" s="174" t="s">
         <v>17</v>
       </c>
-      <c r="BC2" s="164" t="s">
+      <c r="BC2" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="BD2" s="164" t="s">
+      <c r="BD2" s="190" t="s">
         <v>19</v>
       </c>
-      <c r="BE2" s="164" t="s">
+      <c r="BE2" s="190" t="s">
         <v>20</v>
       </c>
-      <c r="BF2" s="164" t="s">
+      <c r="BF2" s="190" t="s">
         <v>21</v>
       </c>
-      <c r="BG2" s="166" t="s">
+      <c r="BG2" s="192" t="s">
         <v>22</v>
       </c>
       <c r="BH2" s="5"/>
-      <c r="BI2" s="162" t="s">
+      <c r="BI2" s="174" t="s">
         <v>23</v>
       </c>
-      <c r="BJ2" s="162" t="s">
+      <c r="BJ2" s="174" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="3:70" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="D3" s="6" t="s">
         <v>25</v>
       </c>
@@ -5809,14 +5818,14 @@
         <v>41</v>
       </c>
       <c r="W3" s="10"/>
-      <c r="X3" s="187"/>
+      <c r="X3" s="167"/>
       <c r="Y3" s="11" t="s">
         <v>42</v>
       </c>
       <c r="Z3" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="AA3" s="191"/>
+      <c r="AA3" s="171"/>
       <c r="AB3" s="13" t="s">
         <v>44</v>
       </c>
@@ -5841,7 +5850,7 @@
       <c r="AI3" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="AJ3" s="171"/>
+      <c r="AJ3" s="181"/>
       <c r="AK3" s="20" t="s">
         <v>52</v>
       </c>
@@ -5875,23 +5884,23 @@
       <c r="AU3" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="AV3" s="171"/>
-      <c r="AW3" s="173"/>
-      <c r="AX3" s="173"/>
-      <c r="AY3" s="175"/>
-      <c r="AZ3" s="163"/>
+      <c r="AV3" s="181"/>
+      <c r="AW3" s="187"/>
+      <c r="AX3" s="187"/>
+      <c r="AY3" s="189"/>
+      <c r="AZ3" s="175"/>
       <c r="BA3" s="28"/>
       <c r="BB3" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="BC3" s="165"/>
-      <c r="BD3" s="165"/>
-      <c r="BE3" s="165"/>
-      <c r="BF3" s="165"/>
-      <c r="BG3" s="167"/>
+      <c r="BC3" s="191"/>
+      <c r="BD3" s="191"/>
+      <c r="BE3" s="191"/>
+      <c r="BF3" s="191"/>
+      <c r="BG3" s="193"/>
       <c r="BH3" s="5"/>
-      <c r="BI3" s="163"/>
-      <c r="BJ3" s="163"/>
+      <c r="BI3" s="175"/>
+      <c r="BJ3" s="175"/>
       <c r="BO3" s="29"/>
       <c r="BP3" s="29"/>
       <c r="BQ3" s="29"/>
@@ -6085,7 +6094,7 @@
       <c r="C6" s="36">
         <v>34</v>
       </c>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="82" t="s">
         <v>77</v>
       </c>
       <c r="E6" s="67" t="s">
@@ -6206,7 +6215,7 @@
       <c r="C7" s="36">
         <v>37</v>
       </c>
-      <c r="D7" s="67" t="s">
+      <c r="D7" s="82" t="s">
         <v>81</v>
       </c>
       <c r="E7" s="67" t="s">
@@ -6353,7 +6362,7 @@
       <c r="C8" s="36">
         <v>40</v>
       </c>
-      <c r="D8" s="67" t="s">
+      <c r="D8" s="82" t="s">
         <v>86</v>
       </c>
       <c r="E8" s="67" t="s">
@@ -6502,7 +6511,7 @@
       <c r="C9" s="36">
         <v>42</v>
       </c>
-      <c r="D9" s="67" t="s">
+      <c r="D9" s="82" t="s">
         <v>91</v>
       </c>
       <c r="E9" s="67" t="s">
@@ -6652,7 +6661,7 @@
       <c r="C10" s="36">
         <v>57</v>
       </c>
-      <c r="D10" s="67" t="s">
+      <c r="D10" s="82" t="s">
         <v>95</v>
       </c>
       <c r="E10" s="67" t="s">
@@ -6773,11 +6782,11 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="3:70" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:70" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="36">
         <v>65</v>
       </c>
-      <c r="D11" s="67" t="s">
+      <c r="D11" s="82" t="s">
         <v>99</v>
       </c>
       <c r="E11" s="67"/>
@@ -6886,11 +6895,11 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="3:70" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:70" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C12" s="36">
         <v>69</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="82" t="s">
         <v>102</v>
       </c>
       <c r="E12" s="67"/>
@@ -7003,7 +7012,7 @@
       <c r="C13" s="36">
         <v>70</v>
       </c>
-      <c r="D13" s="67" t="s">
+      <c r="D13" s="82" t="s">
         <v>105</v>
       </c>
       <c r="E13" s="67"/>
@@ -7128,7 +7137,7 @@
     </row>
     <row r="17" spans="3:61" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C17" s="49"/>
-      <c r="D17" t="s">
+      <c r="D17" s="213" t="s">
         <v>108</v>
       </c>
       <c r="BI17"/>
@@ -7138,7 +7147,7 @@
     </row>
     <row r="19" spans="3:61" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="77"/>
-      <c r="D19" t="s">
+      <c r="D19" s="213" t="s">
         <v>109</v>
       </c>
       <c r="BI19"/>
@@ -7173,20 +7182,21 @@
       <c r="U21"/>
       <c r="BI21"/>
     </row>
-    <row r="23" spans="3:61" x14ac:dyDescent="0.25">
-      <c r="D23" t="s">
+    <row r="23" spans="3:61" ht="90" x14ac:dyDescent="0.25">
+      <c r="D23" s="213" t="s">
         <v>110</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="D4:BR13" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="25">
-    <mergeCell ref="AD2:AE2"/>
-    <mergeCell ref="J2:V2"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="BJ2:BJ3"/>
+    <mergeCell ref="BC2:BC3"/>
+    <mergeCell ref="BD2:BD3"/>
+    <mergeCell ref="BE2:BE3"/>
+    <mergeCell ref="BF2:BF3"/>
+    <mergeCell ref="BG2:BG3"/>
+    <mergeCell ref="BI2:BI3"/>
     <mergeCell ref="AZ2:AZ3"/>
     <mergeCell ref="AF2:AG2"/>
     <mergeCell ref="AH2:AI2"/>
@@ -7199,13 +7209,12 @@
     <mergeCell ref="AW2:AW3"/>
     <mergeCell ref="AX2:AX3"/>
     <mergeCell ref="AY2:AY3"/>
-    <mergeCell ref="BJ2:BJ3"/>
-    <mergeCell ref="BC2:BC3"/>
-    <mergeCell ref="BD2:BD3"/>
-    <mergeCell ref="BE2:BE3"/>
-    <mergeCell ref="BF2:BF3"/>
-    <mergeCell ref="BG2:BG3"/>
-    <mergeCell ref="BI2:BI3"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="J2:V2"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AC2"/>
   </mergeCells>
   <conditionalFormatting sqref="J5:J13 M5:S13">
     <cfRule type="containsText" dxfId="296" priority="43" operator="containsText" text="1">
@@ -7395,101 +7404,101 @@
   <sheetData>
     <row r="8" spans="2:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:59" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I9" s="184"/>
-      <c r="J9" s="184"/>
-      <c r="K9" s="184"/>
-      <c r="L9" s="184"/>
-      <c r="M9" s="184"/>
-      <c r="N9" s="184"/>
-      <c r="O9" s="184"/>
-      <c r="P9" s="184"/>
-      <c r="Q9" s="184"/>
-      <c r="R9" s="184"/>
-      <c r="S9" s="184"/>
-      <c r="T9" s="184"/>
-      <c r="U9" s="185"/>
+      <c r="I9" s="164"/>
+      <c r="J9" s="164"/>
+      <c r="K9" s="164"/>
+      <c r="L9" s="164"/>
+      <c r="M9" s="164"/>
+      <c r="N9" s="164"/>
+      <c r="O9" s="164"/>
+      <c r="P9" s="164"/>
+      <c r="Q9" s="164"/>
+      <c r="R9" s="164"/>
+      <c r="S9" s="164"/>
+      <c r="T9" s="164"/>
+      <c r="U9" s="165"/>
       <c r="V9" s="4"/>
-      <c r="W9" s="186" t="s">
-        <v>2</v>
-      </c>
-      <c r="X9" s="196" t="s">
+      <c r="W9" s="166" t="s">
+        <v>2</v>
+      </c>
+      <c r="X9" s="194" t="s">
         <v>3</v>
       </c>
-      <c r="Y9" s="197"/>
-      <c r="Z9" s="190" t="s">
+      <c r="Y9" s="195"/>
+      <c r="Z9" s="170" t="s">
         <v>4</v>
       </c>
-      <c r="AA9" s="192" t="s">
+      <c r="AA9" s="172" t="s">
         <v>5</v>
       </c>
-      <c r="AB9" s="193"/>
-      <c r="AC9" s="181" t="s">
+      <c r="AB9" s="173"/>
+      <c r="AC9" s="162" t="s">
         <v>6</v>
       </c>
-      <c r="AD9" s="182"/>
+      <c r="AD9" s="163"/>
       <c r="AE9" s="176" t="s">
         <v>7</v>
       </c>
       <c r="AF9" s="177"/>
-      <c r="AG9" s="168" t="s">
+      <c r="AG9" s="178" t="s">
         <v>8</v>
       </c>
-      <c r="AH9" s="169"/>
-      <c r="AI9" s="170" t="s">
+      <c r="AH9" s="179"/>
+      <c r="AI9" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="AJ9" s="178" t="s">
+      <c r="AJ9" s="182" t="s">
         <v>10</v>
       </c>
-      <c r="AK9" s="179"/>
-      <c r="AL9" s="180"/>
-      <c r="AM9" s="181" t="s">
+      <c r="AK9" s="183"/>
+      <c r="AL9" s="184"/>
+      <c r="AM9" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="AN9" s="182"/>
+      <c r="AN9" s="163"/>
       <c r="AO9" s="176" t="s">
         <v>12</v>
       </c>
       <c r="AP9" s="177"/>
-      <c r="AQ9" s="168" t="s">
+      <c r="AQ9" s="178" t="s">
         <v>13</v>
       </c>
-      <c r="AR9" s="169"/>
-      <c r="AS9" s="170" t="s">
+      <c r="AR9" s="179"/>
+      <c r="AS9" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="AT9" s="172" t="s">
+      <c r="AT9" s="186" t="s">
         <v>14</v>
       </c>
-      <c r="AU9" s="172" t="s">
+      <c r="AU9" s="186" t="s">
         <v>15</v>
       </c>
-      <c r="AV9" s="174" t="s">
+      <c r="AV9" s="188" t="s">
         <v>16</v>
       </c>
-      <c r="AW9" s="162" t="s">
+      <c r="AW9" s="174" t="s">
         <v>17</v>
       </c>
-      <c r="AZ9" s="164" t="s">
+      <c r="AZ9" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="BA9" s="164" t="s">
+      <c r="BA9" s="190" t="s">
         <v>19</v>
       </c>
-      <c r="BB9" s="164" t="s">
+      <c r="BB9" s="190" t="s">
         <v>20</v>
       </c>
-      <c r="BC9" s="164" t="s">
+      <c r="BC9" s="190" t="s">
         <v>21</v>
       </c>
-      <c r="BD9" s="194" t="s">
+      <c r="BD9" s="196" t="s">
         <v>22</v>
       </c>
       <c r="BE9" s="5"/>
-      <c r="BF9" s="162" t="s">
+      <c r="BF9" s="174" t="s">
         <v>23</v>
       </c>
-      <c r="BG9" s="162" t="s">
+      <c r="BG9" s="174" t="s">
         <v>24</v>
       </c>
     </row>
@@ -7548,14 +7557,14 @@
         <v>41</v>
       </c>
       <c r="V10" s="10"/>
-      <c r="W10" s="187"/>
+      <c r="W10" s="167"/>
       <c r="X10" s="78" t="s">
         <v>42</v>
       </c>
       <c r="Y10" s="79" t="s">
         <v>43</v>
       </c>
-      <c r="Z10" s="191"/>
+      <c r="Z10" s="171"/>
       <c r="AA10" s="13" t="s">
         <v>44</v>
       </c>
@@ -7580,7 +7589,7 @@
       <c r="AH10" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="AI10" s="171"/>
+      <c r="AI10" s="181"/>
       <c r="AJ10" s="20" t="s">
         <v>52</v>
       </c>
@@ -7608,23 +7617,23 @@
       <c r="AR10" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="AS10" s="171"/>
-      <c r="AT10" s="173"/>
-      <c r="AU10" s="173"/>
-      <c r="AV10" s="175"/>
-      <c r="AW10" s="163"/>
+      <c r="AS10" s="181"/>
+      <c r="AT10" s="187"/>
+      <c r="AU10" s="187"/>
+      <c r="AV10" s="189"/>
+      <c r="AW10" s="175"/>
       <c r="AX10" s="28"/>
       <c r="AY10" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="AZ10" s="165"/>
-      <c r="BA10" s="165"/>
-      <c r="BB10" s="165"/>
-      <c r="BC10" s="165"/>
-      <c r="BD10" s="195"/>
+      <c r="AZ10" s="191"/>
+      <c r="BA10" s="191"/>
+      <c r="BB10" s="191"/>
+      <c r="BC10" s="191"/>
+      <c r="BD10" s="197"/>
       <c r="BE10" s="5"/>
-      <c r="BF10" s="163"/>
-      <c r="BG10" s="163"/>
+      <c r="BF10" s="175"/>
+      <c r="BG10" s="175"/>
     </row>
     <row r="11" spans="2:59" x14ac:dyDescent="0.25">
       <c r="C11" s="32"/>
@@ -7889,12 +7898,13 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="AC9:AD9"/>
-    <mergeCell ref="I9:U9"/>
-    <mergeCell ref="W9:W10"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="Z9:Z10"/>
-    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="BG9:BG10"/>
+    <mergeCell ref="AZ9:AZ10"/>
+    <mergeCell ref="BA9:BA10"/>
+    <mergeCell ref="BB9:BB10"/>
+    <mergeCell ref="BC9:BC10"/>
+    <mergeCell ref="BD9:BD10"/>
+    <mergeCell ref="BF9:BF10"/>
     <mergeCell ref="AW9:AW10"/>
     <mergeCell ref="AE9:AF9"/>
     <mergeCell ref="AG9:AH9"/>
@@ -7907,13 +7917,12 @@
     <mergeCell ref="AT9:AT10"/>
     <mergeCell ref="AU9:AU10"/>
     <mergeCell ref="AV9:AV10"/>
-    <mergeCell ref="BG9:BG10"/>
-    <mergeCell ref="AZ9:AZ10"/>
-    <mergeCell ref="BA9:BA10"/>
-    <mergeCell ref="BB9:BB10"/>
-    <mergeCell ref="BC9:BC10"/>
-    <mergeCell ref="BD9:BD10"/>
-    <mergeCell ref="BF9:BF10"/>
+    <mergeCell ref="AC9:AD9"/>
+    <mergeCell ref="I9:U9"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="AA9:AB9"/>
   </mergeCells>
   <conditionalFormatting sqref="I12 L12:R12">
     <cfRule type="containsText" dxfId="269" priority="57" operator="containsText" text="1">
@@ -8207,101 +8216,101 @@
   <sheetData>
     <row r="8" spans="2:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I9" s="184"/>
-      <c r="J9" s="184"/>
-      <c r="K9" s="184"/>
-      <c r="L9" s="184"/>
-      <c r="M9" s="184"/>
-      <c r="N9" s="184"/>
-      <c r="O9" s="184"/>
-      <c r="P9" s="184"/>
-      <c r="Q9" s="184"/>
-      <c r="R9" s="184"/>
-      <c r="S9" s="184"/>
-      <c r="T9" s="184"/>
-      <c r="U9" s="185"/>
+      <c r="I9" s="164"/>
+      <c r="J9" s="164"/>
+      <c r="K9" s="164"/>
+      <c r="L9" s="164"/>
+      <c r="M9" s="164"/>
+      <c r="N9" s="164"/>
+      <c r="O9" s="164"/>
+      <c r="P9" s="164"/>
+      <c r="Q9" s="164"/>
+      <c r="R9" s="164"/>
+      <c r="S9" s="164"/>
+      <c r="T9" s="164"/>
+      <c r="U9" s="165"/>
       <c r="V9" s="4"/>
-      <c r="W9" s="186" t="s">
-        <v>2</v>
-      </c>
-      <c r="X9" s="188" t="s">
+      <c r="W9" s="166" t="s">
+        <v>2</v>
+      </c>
+      <c r="X9" s="168" t="s">
         <v>3</v>
       </c>
-      <c r="Y9" s="189"/>
-      <c r="Z9" s="190" t="s">
+      <c r="Y9" s="169"/>
+      <c r="Z9" s="170" t="s">
         <v>4</v>
       </c>
-      <c r="AA9" s="192" t="s">
+      <c r="AA9" s="172" t="s">
         <v>5</v>
       </c>
-      <c r="AB9" s="193"/>
-      <c r="AC9" s="181" t="s">
+      <c r="AB9" s="173"/>
+      <c r="AC9" s="162" t="s">
         <v>6</v>
       </c>
-      <c r="AD9" s="182"/>
+      <c r="AD9" s="163"/>
       <c r="AE9" s="176" t="s">
         <v>7</v>
       </c>
       <c r="AF9" s="177"/>
-      <c r="AG9" s="168" t="s">
+      <c r="AG9" s="178" t="s">
         <v>8</v>
       </c>
-      <c r="AH9" s="169"/>
-      <c r="AI9" s="170" t="s">
+      <c r="AH9" s="179"/>
+      <c r="AI9" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="AJ9" s="178" t="s">
+      <c r="AJ9" s="182" t="s">
         <v>10</v>
       </c>
-      <c r="AK9" s="179"/>
-      <c r="AL9" s="180"/>
-      <c r="AM9" s="181" t="s">
+      <c r="AK9" s="183"/>
+      <c r="AL9" s="184"/>
+      <c r="AM9" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="AN9" s="182"/>
+      <c r="AN9" s="163"/>
       <c r="AO9" s="176" t="s">
         <v>12</v>
       </c>
       <c r="AP9" s="177"/>
-      <c r="AQ9" s="168" t="s">
+      <c r="AQ9" s="178" t="s">
         <v>13</v>
       </c>
-      <c r="AR9" s="169"/>
-      <c r="AS9" s="170" t="s">
+      <c r="AR9" s="179"/>
+      <c r="AS9" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="AT9" s="172" t="s">
+      <c r="AT9" s="186" t="s">
         <v>14</v>
       </c>
-      <c r="AU9" s="172" t="s">
+      <c r="AU9" s="186" t="s">
         <v>15</v>
       </c>
-      <c r="AV9" s="174" t="s">
+      <c r="AV9" s="188" t="s">
         <v>16</v>
       </c>
-      <c r="AW9" s="162" t="s">
+      <c r="AW9" s="174" t="s">
         <v>17</v>
       </c>
-      <c r="AY9" s="164" t="s">
+      <c r="AY9" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="AZ9" s="164" t="s">
+      <c r="AZ9" s="190" t="s">
         <v>19</v>
       </c>
-      <c r="BA9" s="164" t="s">
+      <c r="BA9" s="190" t="s">
         <v>20</v>
       </c>
-      <c r="BB9" s="164" t="s">
+      <c r="BB9" s="190" t="s">
         <v>21</v>
       </c>
-      <c r="BC9" s="194" t="s">
+      <c r="BC9" s="196" t="s">
         <v>22</v>
       </c>
       <c r="BD9" s="5"/>
-      <c r="BE9" s="162" t="s">
+      <c r="BE9" s="174" t="s">
         <v>23</v>
       </c>
-      <c r="BF9" s="162" t="s">
+      <c r="BF9" s="174" t="s">
         <v>24</v>
       </c>
     </row>
@@ -8360,14 +8369,14 @@
         <v>41</v>
       </c>
       <c r="V10" s="10"/>
-      <c r="W10" s="187"/>
+      <c r="W10" s="167"/>
       <c r="X10" s="11" t="s">
         <v>42</v>
       </c>
       <c r="Y10" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="Z10" s="191"/>
+      <c r="Z10" s="171"/>
       <c r="AA10" s="95" t="s">
         <v>44</v>
       </c>
@@ -8392,7 +8401,7 @@
       <c r="AH10" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="AI10" s="171"/>
+      <c r="AI10" s="181"/>
       <c r="AJ10" s="20" t="s">
         <v>52</v>
       </c>
@@ -8420,20 +8429,20 @@
       <c r="AR10" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="AS10" s="171"/>
-      <c r="AT10" s="173"/>
-      <c r="AU10" s="173"/>
-      <c r="AV10" s="175"/>
-      <c r="AW10" s="163"/>
+      <c r="AS10" s="181"/>
+      <c r="AT10" s="187"/>
+      <c r="AU10" s="187"/>
+      <c r="AV10" s="189"/>
+      <c r="AW10" s="175"/>
       <c r="AX10" s="28"/>
-      <c r="AY10" s="165"/>
-      <c r="AZ10" s="165"/>
-      <c r="BA10" s="165"/>
-      <c r="BB10" s="165"/>
-      <c r="BC10" s="195"/>
+      <c r="AY10" s="191"/>
+      <c r="AZ10" s="191"/>
+      <c r="BA10" s="191"/>
+      <c r="BB10" s="191"/>
+      <c r="BC10" s="197"/>
       <c r="BD10" s="5"/>
-      <c r="BE10" s="163"/>
-      <c r="BF10" s="163"/>
+      <c r="BE10" s="175"/>
+      <c r="BF10" s="175"/>
     </row>
     <row r="11" spans="2:58" x14ac:dyDescent="0.25">
       <c r="C11" s="32"/>
@@ -8766,12 +8775,13 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="AC9:AD9"/>
-    <mergeCell ref="I9:U9"/>
-    <mergeCell ref="W9:W10"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="Z9:Z10"/>
-    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="BF9:BF10"/>
+    <mergeCell ref="AY9:AY10"/>
+    <mergeCell ref="AZ9:AZ10"/>
+    <mergeCell ref="BA9:BA10"/>
+    <mergeCell ref="BB9:BB10"/>
+    <mergeCell ref="BC9:BC10"/>
+    <mergeCell ref="BE9:BE10"/>
     <mergeCell ref="AW9:AW10"/>
     <mergeCell ref="AE9:AF9"/>
     <mergeCell ref="AG9:AH9"/>
@@ -8784,13 +8794,12 @@
     <mergeCell ref="AT9:AT10"/>
     <mergeCell ref="AU9:AU10"/>
     <mergeCell ref="AV9:AV10"/>
-    <mergeCell ref="BF9:BF10"/>
-    <mergeCell ref="AY9:AY10"/>
-    <mergeCell ref="AZ9:AZ10"/>
-    <mergeCell ref="BA9:BA10"/>
-    <mergeCell ref="BB9:BB10"/>
-    <mergeCell ref="BC9:BC10"/>
-    <mergeCell ref="BE9:BE10"/>
+    <mergeCell ref="AC9:AD9"/>
+    <mergeCell ref="I9:U9"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="AA9:AB9"/>
   </mergeCells>
   <conditionalFormatting sqref="I12 L12:R12">
     <cfRule type="containsText" dxfId="209" priority="57" operator="containsText" text="1">
@@ -9086,101 +9095,101 @@
   <sheetData>
     <row r="8" spans="2:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I9" s="184"/>
-      <c r="J9" s="184"/>
-      <c r="K9" s="184"/>
-      <c r="L9" s="184"/>
-      <c r="M9" s="184"/>
-      <c r="N9" s="184"/>
-      <c r="O9" s="184"/>
-      <c r="P9" s="184"/>
-      <c r="Q9" s="184"/>
-      <c r="R9" s="184"/>
-      <c r="S9" s="184"/>
-      <c r="T9" s="184"/>
-      <c r="U9" s="185"/>
+      <c r="I9" s="164"/>
+      <c r="J9" s="164"/>
+      <c r="K9" s="164"/>
+      <c r="L9" s="164"/>
+      <c r="M9" s="164"/>
+      <c r="N9" s="164"/>
+      <c r="O9" s="164"/>
+      <c r="P9" s="164"/>
+      <c r="Q9" s="164"/>
+      <c r="R9" s="164"/>
+      <c r="S9" s="164"/>
+      <c r="T9" s="164"/>
+      <c r="U9" s="165"/>
       <c r="V9" s="4"/>
-      <c r="W9" s="186" t="s">
-        <v>2</v>
-      </c>
-      <c r="X9" s="188" t="s">
+      <c r="W9" s="166" t="s">
+        <v>2</v>
+      </c>
+      <c r="X9" s="168" t="s">
         <v>3</v>
       </c>
-      <c r="Y9" s="189"/>
-      <c r="Z9" s="190" t="s">
+      <c r="Y9" s="169"/>
+      <c r="Z9" s="170" t="s">
         <v>4</v>
       </c>
-      <c r="AA9" s="192" t="s">
+      <c r="AA9" s="172" t="s">
         <v>5</v>
       </c>
-      <c r="AB9" s="193"/>
-      <c r="AC9" s="181" t="s">
+      <c r="AB9" s="173"/>
+      <c r="AC9" s="162" t="s">
         <v>6</v>
       </c>
-      <c r="AD9" s="182"/>
+      <c r="AD9" s="163"/>
       <c r="AE9" s="176" t="s">
         <v>7</v>
       </c>
       <c r="AF9" s="177"/>
-      <c r="AG9" s="168" t="s">
+      <c r="AG9" s="178" t="s">
         <v>8</v>
       </c>
-      <c r="AH9" s="169"/>
-      <c r="AI9" s="170" t="s">
+      <c r="AH9" s="179"/>
+      <c r="AI9" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="AJ9" s="178" t="s">
+      <c r="AJ9" s="182" t="s">
         <v>10</v>
       </c>
-      <c r="AK9" s="179"/>
-      <c r="AL9" s="180"/>
-      <c r="AM9" s="181" t="s">
+      <c r="AK9" s="183"/>
+      <c r="AL9" s="184"/>
+      <c r="AM9" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="AN9" s="182"/>
+      <c r="AN9" s="163"/>
       <c r="AO9" s="176" t="s">
         <v>12</v>
       </c>
       <c r="AP9" s="177"/>
-      <c r="AQ9" s="168" t="s">
+      <c r="AQ9" s="178" t="s">
         <v>13</v>
       </c>
-      <c r="AR9" s="169"/>
-      <c r="AS9" s="170" t="s">
+      <c r="AR9" s="179"/>
+      <c r="AS9" s="180" t="s">
         <v>9</v>
       </c>
-      <c r="AT9" s="172" t="s">
+      <c r="AT9" s="186" t="s">
         <v>14</v>
       </c>
-      <c r="AU9" s="172" t="s">
+      <c r="AU9" s="186" t="s">
         <v>15</v>
       </c>
-      <c r="AV9" s="174" t="s">
+      <c r="AV9" s="188" t="s">
         <v>16</v>
       </c>
-      <c r="AW9" s="162" t="s">
+      <c r="AW9" s="174" t="s">
         <v>17</v>
       </c>
-      <c r="AY9" s="164" t="s">
+      <c r="AY9" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="AZ9" s="164" t="s">
+      <c r="AZ9" s="190" t="s">
         <v>19</v>
       </c>
-      <c r="BA9" s="164" t="s">
+      <c r="BA9" s="190" t="s">
         <v>20</v>
       </c>
-      <c r="BB9" s="164" t="s">
+      <c r="BB9" s="190" t="s">
         <v>21</v>
       </c>
-      <c r="BC9" s="194" t="s">
+      <c r="BC9" s="196" t="s">
         <v>22</v>
       </c>
       <c r="BD9" s="5"/>
-      <c r="BE9" s="162" t="s">
+      <c r="BE9" s="174" t="s">
         <v>23</v>
       </c>
-      <c r="BF9" s="162" t="s">
+      <c r="BF9" s="174" t="s">
         <v>24</v>
       </c>
     </row>
@@ -9239,14 +9248,14 @@
         <v>41</v>
       </c>
       <c r="V10" s="10"/>
-      <c r="W10" s="187"/>
+      <c r="W10" s="167"/>
       <c r="X10" s="11" t="s">
         <v>42</v>
       </c>
       <c r="Y10" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="Z10" s="191"/>
+      <c r="Z10" s="171"/>
       <c r="AA10" s="95" t="s">
         <v>44</v>
       </c>
@@ -9271,7 +9280,7 @@
       <c r="AH10" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="AI10" s="171"/>
+      <c r="AI10" s="181"/>
       <c r="AJ10" s="20" t="s">
         <v>52</v>
       </c>
@@ -9299,20 +9308,20 @@
       <c r="AR10" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="AS10" s="171"/>
-      <c r="AT10" s="173"/>
-      <c r="AU10" s="173"/>
-      <c r="AV10" s="175"/>
-      <c r="AW10" s="163"/>
+      <c r="AS10" s="181"/>
+      <c r="AT10" s="187"/>
+      <c r="AU10" s="187"/>
+      <c r="AV10" s="189"/>
+      <c r="AW10" s="175"/>
       <c r="AX10" s="28"/>
-      <c r="AY10" s="165"/>
-      <c r="AZ10" s="165"/>
-      <c r="BA10" s="165"/>
-      <c r="BB10" s="165"/>
-      <c r="BC10" s="195"/>
+      <c r="AY10" s="191"/>
+      <c r="AZ10" s="191"/>
+      <c r="BA10" s="191"/>
+      <c r="BB10" s="191"/>
+      <c r="BC10" s="197"/>
       <c r="BD10" s="5"/>
-      <c r="BE10" s="163"/>
-      <c r="BF10" s="163"/>
+      <c r="BE10" s="175"/>
+      <c r="BF10" s="175"/>
     </row>
     <row r="11" spans="2:58" x14ac:dyDescent="0.25">
       <c r="C11" s="32"/>
@@ -9994,12 +10003,13 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="AC9:AD9"/>
-    <mergeCell ref="I9:U9"/>
-    <mergeCell ref="W9:W10"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="Z9:Z10"/>
-    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="BF9:BF10"/>
+    <mergeCell ref="AY9:AY10"/>
+    <mergeCell ref="AZ9:AZ10"/>
+    <mergeCell ref="BA9:BA10"/>
+    <mergeCell ref="BB9:BB10"/>
+    <mergeCell ref="BC9:BC10"/>
+    <mergeCell ref="BE9:BE10"/>
     <mergeCell ref="AW9:AW10"/>
     <mergeCell ref="AE9:AF9"/>
     <mergeCell ref="AG9:AH9"/>
@@ -10012,13 +10022,12 @@
     <mergeCell ref="AT9:AT10"/>
     <mergeCell ref="AU9:AU10"/>
     <mergeCell ref="AV9:AV10"/>
-    <mergeCell ref="BF9:BF10"/>
-    <mergeCell ref="AY9:AY10"/>
-    <mergeCell ref="AZ9:AZ10"/>
-    <mergeCell ref="BA9:BA10"/>
-    <mergeCell ref="BB9:BB10"/>
-    <mergeCell ref="BC9:BC10"/>
-    <mergeCell ref="BE9:BE10"/>
+    <mergeCell ref="AC9:AD9"/>
+    <mergeCell ref="I9:U9"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="AA9:AB9"/>
   </mergeCells>
   <conditionalFormatting sqref="I12 L12:R12">
     <cfRule type="containsText" dxfId="149" priority="117" operator="containsText" text="1">
@@ -10544,101 +10553,101 @@
   <sheetData>
     <row r="8" spans="2:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:58" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I9" s="184"/>
-      <c r="J9" s="184"/>
-      <c r="K9" s="184"/>
-      <c r="L9" s="184"/>
-      <c r="M9" s="184"/>
-      <c r="N9" s="184"/>
-      <c r="O9" s="184"/>
-      <c r="P9" s="184"/>
-      <c r="Q9" s="184"/>
-      <c r="R9" s="184"/>
-      <c r="S9" s="184"/>
-      <c r="T9" s="184"/>
-      <c r="U9" s="185"/>
+      <c r="I9" s="164"/>
+      <c r="J9" s="164"/>
+      <c r="K9" s="164"/>
+      <c r="L9" s="164"/>
+      <c r="M9" s="164"/>
+      <c r="N9" s="164"/>
+      <c r="O9" s="164"/>
+      <c r="P9" s="164"/>
+      <c r="Q9" s="164"/>
+      <c r="R9" s="164"/>
+      <c r="S9" s="164"/>
+      <c r="T9" s="164"/>
+      <c r="U9" s="165"/>
       <c r="V9" s="4"/>
-      <c r="W9" s="186" t="s">
-        <v>2</v>
-      </c>
-      <c r="X9" s="188" t="s">
+      <c r="W9" s="166" t="s">
+        <v>2</v>
+      </c>
+      <c r="X9" s="168" t="s">
         <v>3</v>
       </c>
-      <c r="Y9" s="189"/>
-      <c r="Z9" s="190" t="s">
+      <c r="Y9" s="169"/>
+      <c r="Z9" s="170" t="s">
         <v>4</v>
       </c>
-      <c r="AA9" s="211" t="s">
+      <c r="AA9" s="200" t="s">
         <v>5</v>
       </c>
-      <c r="AB9" s="212"/>
-      <c r="AC9" s="209" t="s">
+      <c r="AB9" s="201"/>
+      <c r="AC9" s="198" t="s">
         <v>6</v>
       </c>
-      <c r="AD9" s="210"/>
-      <c r="AE9" s="204" t="s">
+      <c r="AD9" s="199"/>
+      <c r="AE9" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="AF9" s="205"/>
-      <c r="AG9" s="198" t="s">
+      <c r="AF9" s="203"/>
+      <c r="AG9" s="204" t="s">
         <v>8</v>
       </c>
-      <c r="AH9" s="199"/>
-      <c r="AI9" s="200" t="s">
+      <c r="AH9" s="205"/>
+      <c r="AI9" s="206" t="s">
         <v>9</v>
       </c>
-      <c r="AJ9" s="206" t="s">
+      <c r="AJ9" s="208" t="s">
         <v>10</v>
       </c>
-      <c r="AK9" s="207"/>
-      <c r="AL9" s="208"/>
-      <c r="AM9" s="209" t="s">
+      <c r="AK9" s="209"/>
+      <c r="AL9" s="210"/>
+      <c r="AM9" s="198" t="s">
         <v>11</v>
       </c>
-      <c r="AN9" s="210"/>
-      <c r="AO9" s="204" t="s">
+      <c r="AN9" s="199"/>
+      <c r="AO9" s="202" t="s">
         <v>12</v>
       </c>
-      <c r="AP9" s="205"/>
-      <c r="AQ9" s="198" t="s">
+      <c r="AP9" s="203"/>
+      <c r="AQ9" s="204" t="s">
         <v>13</v>
       </c>
-      <c r="AR9" s="199"/>
-      <c r="AS9" s="200" t="s">
+      <c r="AR9" s="205"/>
+      <c r="AS9" s="206" t="s">
         <v>9</v>
       </c>
-      <c r="AT9" s="202" t="s">
+      <c r="AT9" s="211" t="s">
         <v>14</v>
       </c>
-      <c r="AU9" s="202" t="s">
+      <c r="AU9" s="211" t="s">
         <v>15</v>
       </c>
-      <c r="AV9" s="174" t="s">
+      <c r="AV9" s="188" t="s">
         <v>16</v>
       </c>
-      <c r="AW9" s="162" t="s">
+      <c r="AW9" s="174" t="s">
         <v>17</v>
       </c>
-      <c r="AY9" s="164" t="s">
+      <c r="AY9" s="190" t="s">
         <v>18</v>
       </c>
-      <c r="AZ9" s="164" t="s">
+      <c r="AZ9" s="190" t="s">
         <v>19</v>
       </c>
-      <c r="BA9" s="164" t="s">
+      <c r="BA9" s="190" t="s">
         <v>20</v>
       </c>
-      <c r="BB9" s="164" t="s">
+      <c r="BB9" s="190" t="s">
         <v>21</v>
       </c>
-      <c r="BC9" s="194" t="s">
+      <c r="BC9" s="196" t="s">
         <v>22</v>
       </c>
       <c r="BD9" s="5"/>
-      <c r="BE9" s="162" t="s">
+      <c r="BE9" s="174" t="s">
         <v>23</v>
       </c>
-      <c r="BF9" s="162" t="s">
+      <c r="BF9" s="174" t="s">
         <v>24</v>
       </c>
     </row>
@@ -10697,14 +10706,14 @@
         <v>41</v>
       </c>
       <c r="V10" s="10"/>
-      <c r="W10" s="187"/>
+      <c r="W10" s="167"/>
       <c r="X10" s="11" t="s">
         <v>42</v>
       </c>
       <c r="Y10" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="Z10" s="191"/>
+      <c r="Z10" s="171"/>
       <c r="AA10" s="126" t="s">
         <v>44</v>
       </c>
@@ -10729,7 +10738,7 @@
       <c r="AH10" s="132" t="s">
         <v>51</v>
       </c>
-      <c r="AI10" s="201"/>
+      <c r="AI10" s="207"/>
       <c r="AJ10" s="133" t="s">
         <v>52</v>
       </c>
@@ -10757,20 +10766,20 @@
       <c r="AR10" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="AS10" s="201"/>
-      <c r="AT10" s="203"/>
-      <c r="AU10" s="203"/>
-      <c r="AV10" s="175"/>
-      <c r="AW10" s="163"/>
+      <c r="AS10" s="207"/>
+      <c r="AT10" s="212"/>
+      <c r="AU10" s="212"/>
+      <c r="AV10" s="189"/>
+      <c r="AW10" s="175"/>
       <c r="AX10" s="28"/>
-      <c r="AY10" s="165"/>
-      <c r="AZ10" s="165"/>
-      <c r="BA10" s="165"/>
-      <c r="BB10" s="165"/>
-      <c r="BC10" s="195"/>
+      <c r="AY10" s="191"/>
+      <c r="AZ10" s="191"/>
+      <c r="BA10" s="191"/>
+      <c r="BB10" s="191"/>
+      <c r="BC10" s="197"/>
       <c r="BD10" s="5"/>
-      <c r="BE10" s="163"/>
-      <c r="BF10" s="163"/>
+      <c r="BE10" s="175"/>
+      <c r="BF10" s="175"/>
     </row>
     <row r="11" spans="2:58" x14ac:dyDescent="0.25">
       <c r="C11" s="32"/>
@@ -10926,12 +10935,13 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="AC9:AD9"/>
-    <mergeCell ref="I9:U9"/>
-    <mergeCell ref="W9:W10"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="Z9:Z10"/>
-    <mergeCell ref="AA9:AB9"/>
+    <mergeCell ref="BF9:BF10"/>
+    <mergeCell ref="AY9:AY10"/>
+    <mergeCell ref="AZ9:AZ10"/>
+    <mergeCell ref="BA9:BA10"/>
+    <mergeCell ref="BB9:BB10"/>
+    <mergeCell ref="BC9:BC10"/>
+    <mergeCell ref="BE9:BE10"/>
     <mergeCell ref="AW9:AW10"/>
     <mergeCell ref="AE9:AF9"/>
     <mergeCell ref="AG9:AH9"/>
@@ -10944,13 +10954,12 @@
     <mergeCell ref="AT9:AT10"/>
     <mergeCell ref="AU9:AU10"/>
     <mergeCell ref="AV9:AV10"/>
-    <mergeCell ref="BF9:BF10"/>
-    <mergeCell ref="AY9:AY10"/>
-    <mergeCell ref="AZ9:AZ10"/>
-    <mergeCell ref="BA9:BA10"/>
-    <mergeCell ref="BB9:BB10"/>
-    <mergeCell ref="BC9:BC10"/>
-    <mergeCell ref="BE9:BE10"/>
+    <mergeCell ref="AC9:AD9"/>
+    <mergeCell ref="I9:U9"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="AA9:AB9"/>
   </mergeCells>
   <conditionalFormatting sqref="I12 L12:R12">
     <cfRule type="containsText" dxfId="29" priority="27" operator="containsText" text="1">
